--- a/education_forms/044_healthcare_conference_registration_form--education_forms.xlsx
+++ b/education_forms/044_healthcare_conference_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>attendee_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Attendee Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,87 +543,87 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>attending_conferences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Conferences Attending</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>interested_conferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Interested Conferences</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>date_of_arrival</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Date of Arrival</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,173 +658,173 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>time_of_arrival</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Time of Arrival</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>time_of_departure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Time of Departure</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>accommodation_preferences</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Accommodation Preferences</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>transportation_preferences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Transportation Preferences</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Contact Method</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>dietary_requirement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Dietary Requirement</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>medical_requirements</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Medical Requirements</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Special Requests</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>page1</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,102 +896,289 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>attending_conferences_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>attending_conferences_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>interested_conferences_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>interested_conferences_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>accommodation_preferences_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page1_choices</t>
+          <t>accommodation_preferences_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>transportation_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>transportation_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Train</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>transportation_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>flight</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Flight</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>transportation_preferences_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>contact_method_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>contact_method_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>contact_method_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dietary_requirement_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>vegetarian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dietary_requirement_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>vegan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Vegan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dietary_requirement_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>non-vegetarian</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Non-vegetarian</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dietary_requirement_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
